--- a/inventario/Inventario_Keiko.xlsx
+++ b/inventario/Inventario_Keiko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHONY CONTERON\OneDrive\Documentos\GitHub\Tecnicentro_Keiko\inventario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE378A9C-78EF-4146-A533-176CBA9C9177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886A7B72-F74B-4DCC-9BC7-B7CCDA50B8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,12 +366,6 @@
     <t>Filtro de aceite tipo cartucho Advance AOE-9443 para aplicaciones Peugeot y Citroën, según motor y versión.</t>
   </si>
   <si>
-    <t>Peugeot 206, según motor y versión | Peugeot 307, según motor y versión | Citroën C2, según motor y versión | Citroën C3, según motor y versión | Citroën Xsara, según motor y versión</t>
-  </si>
-  <si>
-    <t>ML-9443 | SO011 | MANN HU 612 x | Hengst E35H D102 | OE 1109 AN | Peugeot 1109 R6 | Citroën 1109 R7 | Peugeot 9463704780</t>
-  </si>
-  <si>
     <t>https://distriparteslm.ec/categoria-producto/advance-2/page/21/ | https://www.mann-filter.com/en/catalog/search-results/product.html/hu612x_mann-filter.html | https://catalog.hengst.com/de/online-katalog/produkt/649130000-00/my/</t>
   </si>
   <si>
@@ -384,7 +378,13 @@
     <t>Código y marca confirmados en las fotos. La equivalencia y las aplicaciones coinciden en catálogos técnicos; confirmar año, motor o VIN antes de vender.</t>
   </si>
   <si>
-    <t>Filtro de aceite Advance AOE-9443 con guía. Los catálogos consultados lo relacionan con aplicaciones Peugeot y Citroën y con las equivalencias MANN HU 612 x y Hengst E35H D102. Antes de la entrega se confirma año, motor y versión del vehículo.</t>
+    <t>Peugeot 206, 307, Citroën C2, C3, Xsara. Según motor y versión</t>
+  </si>
+  <si>
+    <t>ML-9443, SO011, MANN HU 612 x, Hengst E35H D102, OE 1109 AN, Peugeot 1109 R6, Citroën 1109 R7, Peugeot 9463704780</t>
+  </si>
+  <si>
+    <t>Filtro de aceite Advance AOE-9443 con guía. Con aplicaciones Peugeot y Citroën y con las equivalencias MANN HU 612 x y Hengst E35H D102. Antes de la entrega se confirma año, motor y versión del vehículo.</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D3" s="4">
         <f>SUM(F7:F506)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>43</v>
       </c>
       <c r="F8" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="13">
         <v>30</v>
@@ -1595,7 +1595,7 @@
       <c r="U13" s="8"/>
     </row>
     <row r="14" spans="1:21" ht="31.95" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="23">
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -1627,16 +1627,16 @@
         <v>116</v>
       </c>
       <c r="L14" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="N14" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="M14" s="10" t="s">
+      <c r="O14" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>37</v>
@@ -1651,10 +1651,10 @@
         <v>8</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="31.95" customHeight="1">

--- a/inventario/Inventario_Keiko.xlsx
+++ b/inventario/Inventario_Keiko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHONY CONTERON\OneDrive\Documentos\GitHub\Tecnicentro_Keiko\inventario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886A7B72-F74B-4DCC-9BC7-B7CCDA50B8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBF72C9-70DF-4191-B816-B228433617D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D3" s="4">
         <f>SUM(F7:F506)</f>
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
@@ -1497,7 +1497,7 @@
         <v>66</v>
       </c>
       <c r="F12" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>50</v>

--- a/inventario/Inventario_Keiko.xlsx
+++ b/inventario/Inventario_Keiko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHONY CONTERON\OneDrive\Documentos\GitHub\Tecnicentro_Keiko\inventario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBF72C9-70DF-4191-B816-B228433617D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE518C2-069C-42E2-8E4A-B6BB60848310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="122">
   <si>
     <t>Inventario de repuestos | Tecnicentro Keiko</t>
   </si>
@@ -385,6 +385,21 @@
   </si>
   <si>
     <t>Filtro de aceite Advance AOE-9443 con guía. Con aplicaciones Peugeot y Citroën y con las equivalencias MANN HU 612 x y Hengst E35H D102. Antes de la entrega se confirma año, motor y versión del vehículo.</t>
+  </si>
+  <si>
+    <t>AFE-15017</t>
+  </si>
+  <si>
+    <t>Filtro de Combustible Hino y Mitsubishi</t>
+  </si>
+  <si>
+    <t>AFT-7864</t>
+  </si>
+  <si>
+    <t>Filtro de Aire</t>
+  </si>
+  <si>
+    <t>SHOGUN</t>
   </si>
 </sst>
 </file>
@@ -738,8 +753,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="InventarioKeiko" displayName="InventarioKeiko" ref="A6:U15" totalsRowShown="0">
-  <autoFilter ref="A6:U15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="InventarioKeiko" displayName="InventarioKeiko" ref="A6:U16" totalsRowShown="0">
+  <autoFilter ref="A6:U16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID interno"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Código"/>
@@ -1044,14 +1059,14 @@
       </c>
       <c r="B3" s="4">
         <f>COUNTIFS(B7:B506,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(F7:F506)</f>
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
@@ -1554,7 +1569,7 @@
         <v>66</v>
       </c>
       <c r="F13" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>50</v>
@@ -1611,7 +1626,7 @@
         <v>43</v>
       </c>
       <c r="F14" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>50</v>
@@ -1658,14 +1673,30 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="31.95" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="9"/>
+      <c r="A15" s="9">
+        <v>9</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="12">
+        <v>5</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="I15" s="9"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
@@ -1681,14 +1712,30 @@
       <c r="U15" s="8"/>
     </row>
     <row r="16" spans="1:21" ht="31.95" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="9"/>
+      <c r="A16" s="9">
+        <v>10</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="12">
+        <v>5</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="I16" s="9"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>

--- a/inventario/Inventario_Keiko.xlsx
+++ b/inventario/Inventario_Keiko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHONY CONTERON\OneDrive\Documentos\GitHub\Tecnicentro_Keiko\inventario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE518C2-069C-42E2-8E4A-B6BB60848310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA820574-E62F-47A4-9EF3-7EC1FA2B4B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/inventario/Inventario_Keiko.xlsx
+++ b/inventario/Inventario_Keiko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHONY CONTERON\OneDrive\Documentos\GitHub\Tecnicentro_Keiko\inventario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA820574-E62F-47A4-9EF3-7EC1FA2B4B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4915E50-507A-44E4-BD8E-E7A8E837E21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="123">
   <si>
     <t>Inventario de repuestos | Tecnicentro Keiko</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>SHOGUN</t>
+  </si>
+  <si>
+    <t>Investigar</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1076,7 @@
       </c>
       <c r="F3" s="4">
         <f>COUNTIFS(P7:P506,"Investigar")+COUNTIFS(P7:P506,"Revisar")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>4</v>
@@ -1704,7 +1707,9 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
+      <c r="P15" s="10" t="s">
+        <v>122</v>
+      </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="14"/>
@@ -1743,7 +1748,9 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
+      <c r="P16" s="10" t="s">
+        <v>122</v>
+      </c>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
       <c r="S16" s="14"/>
